--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/EMBREAGEM COMPLETA 05_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/EMBREAGEM COMPLETA 05_02.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,17 +444,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>EMBREAGEM COMPLETA  TA GP TITAN FAN CG150 1103318</t>
+          <t>EMBREAGEM COMPLETA  GP TITAN FAN CG150 1103318</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
     </row>
@@ -482,7 +472,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +508,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,11 +528,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -566,7 +548,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -587,11 +568,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -612,7 +588,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -633,7 +608,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -654,7 +628,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -675,7 +648,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -696,11 +668,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -721,7 +688,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -738,11 +704,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -759,7 +720,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,7 +740,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,7 +760,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -822,11 +780,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -847,7 +800,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -868,11 +820,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -893,7 +840,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -914,11 +860,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -939,11 +880,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -964,11 +900,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -989,11 +920,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1014,11 +940,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1039,11 +960,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1064,11 +980,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1089,7 +1000,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1110,11 +1020,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1135,11 +1040,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1160,11 +1060,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1185,7 +1080,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1198,7 +1092,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>EMBREAGEM COMPLETA IRON YBR125026039</t>
+          <t>EMBREAGEM COMPLETA IRON YBR125 026039</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1206,7 +1100,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1227,32 +1120,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>7898635122456</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>EMBREAGEM COMPLETA CAUW PCX 2019</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
